--- a/backend/storage/imports/Master_SBM/2. SATUAN BIAYA TRANSPORTASI DARI DKI JAKARTA KE KABUPATEN atau KOTA SEKITAR (ONE WAY  ).xlsx
+++ b/backend/storage/imports/Master_SBM/2. SATUAN BIAYA TRANSPORTASI DARI DKI JAKARTA KE KABUPATEN atau KOTA SEKITAR (ONE WAY  ).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dean Threean Eleazar\Downloads\kebutuhan magang\Projek magang\DITUGASKAN\SBM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC70682-0C13-4D92-9182-162CAF95ED71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FCB9DF-5D18-4AA5-9205-01873B9ACFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F5FD355C-0182-4D6F-87F4-11D57E1D76F8}"/>
   </bookViews>
@@ -334,22 +334,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -702,180 +690,180 @@
       <c r="A1" s="1">
         <v>2</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="9"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="5"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="12">
+      <c r="A3" s="8">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="2">
         <v>284000</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="12">
+      <c r="A4" s="8">
         <v>2</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="B4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="2">
         <v>284000</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
+      <c r="A5" s="8">
         <v>3</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="2">
         <v>300000</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
+      <c r="A6" s="8">
         <v>4</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="2">
         <v>300000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
-        <v>5</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="A7" s="8">
+        <v>5</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="2">
         <v>275000</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
+      <c r="A8" s="8">
         <v>6</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="10" t="s">
+      <c r="B8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="2">
         <v>286000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
+      <c r="A9" s="8">
         <v>7</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="10" t="s">
+      <c r="B9" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="2">
         <v>286000</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
+      <c r="A10" s="8">
         <v>8</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="2">
         <v>310000</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
+      <c r="A11" s="8">
         <v>9</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="10" t="s">
+      <c r="B11" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="2">
         <v>428000</v>
       </c>
     </row>
